--- a/data/satisfaction_detail/2026/1-8月/散客.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/散客.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>9.82684622067767</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>9.969079061685489</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.75</v>
+        <v>9.574978279756733</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.94</v>
+        <v>9.938253692441355</v>
       </c>
     </row>
     <row r="4">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.69</v>
+        <v>9.611659426585579</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.98</v>
+        <v>9.977254561251087</v>
       </c>
     </row>
     <row r="5">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.529999999999999</v>
+        <v>9.242988705473502</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.954509122502172</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.844526498696785</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.916255430060817</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.550000000000001</v>
+        <v>8.861459600347525</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.83</v>
+        <v>9.71672688629118</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.84</v>
+        <v>9.619713292788878</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.948184187662902</v>
       </c>
     </row>
     <row r="9">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.705890529973935</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.98</v>
+        <v>9.993796698523024</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.83</v>
+        <v>9.735873153779321</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.979322328410079</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.91</v>
+        <v>9.964847958297133</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.985525629887055</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>9.99</v>
+        <v>9.99364900086881</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.979322328410079</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.98</v>
+        <v>9.98449174630756</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>10</v>
@@ -631,7 +631,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.91</v>
+        <v>9.964847958297133</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.94</v>
+        <v>9.977254561251087</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.98</v>
+        <v>9.991728931364031</v>
       </c>
     </row>
     <row r="16">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9.98</v>
+        <v>9.991728931364031</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.98</v>
+        <v>9.991728931364031</v>
       </c>
     </row>
     <row r="17">
@@ -670,7 +670,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.94210251954822</v>
       </c>
     </row>
     <row r="18">
@@ -683,7 +683,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.985525629887055</v>
       </c>
     </row>
     <row r="19">
@@ -696,7 +696,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.985525629887055</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9.92</v>
+        <v>9.977236981934114</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.989883103081828</v>
       </c>
     </row>
     <row r="21">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.91</v>
+        <v>9.96712008501594</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.989883103081828</v>
       </c>
     </row>
     <row r="22">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.927586206896551</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9.93</v>
+        <v>9.966206896551723</v>
       </c>
     </row>
     <row r="24">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>9.92</v>
+        <v>9.951724137931034</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.975862068965515</v>
       </c>
     </row>
     <row r="25">
